--- a/apps/web/public/examples/example-merging-bhav.xlsx
+++ b/apps/web/public/examples/example-merging-bhav.xlsx
@@ -181,252 +181,252 @@
     <t>14:45:00 - 15:50:00</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>13:00:00 - 15:30:00</t>
+  </si>
+  <si>
+    <t>SP-0</t>
+  </si>
+  <si>
+    <t>Behavior in Sport</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>10:20:00 - 12:00:00</t>
+  </si>
+  <si>
+    <t>Behavioral Methods</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Models of Change</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:55:00</t>
+  </si>
+  <si>
+    <t>Stochastic Behavior</t>
+  </si>
+  <si>
+    <t>Eli Specimen, Dee Placeholder</t>
+  </si>
+  <si>
+    <t>SectionId</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>AcademicYear</t>
+  </si>
+  <si>
+    <t>MinimumCredits</t>
+  </si>
+  <si>
+    <t>MaximumCredits</t>
+  </si>
+  <si>
+    <t>StartTime</t>
+  </si>
+  <si>
+    <t>MeetingDuration</t>
+  </si>
+  <si>
+    <t>Classroom</t>
+  </si>
+  <si>
+    <t>CourseLevel</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>EnrollmentDay10</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV112-A</t>
+  </si>
+  <si>
+    <t>AY25</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV112-B</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV212-A</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV312-A</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>AY25-WI-BHAV121-A</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV112-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV219-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-BHAV112-A</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Load</t>
+  </si>
+  <si>
+    <t>AY</t>
+  </si>
+  <si>
+    <t>Constraint</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>Instructor</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Choose</t>
+  </si>
+  <si>
+    <t>Bound</t>
+  </si>
+  <si>
+    <t>Gap</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Starts</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>DayRule</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Should</t>
+  </si>
+  <si>
+    <t>Meets</t>
+  </si>
+  <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Intensive terms meet daily</t>
+  </si>
+  <si>
+    <t>standard</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>WI, SU</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
+  </si>
+  <si>
+    <t>allow</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>StartWeek</t>
+  </si>
+  <si>
+    <t>EndWeek</t>
+  </si>
+  <si>
+    <t>SpreadTerm</t>
+  </si>
+  <si>
+    <t>NonRoom</t>
+  </si>
+  <si>
+    <t>Off Campus</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Fall</t>
+  </si>
+  <si>
     <t>WI</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>13:00:00 - 15:30:00</t>
-  </si>
-  <si>
-    <t>WI-Full</t>
-  </si>
-  <si>
-    <t>Behavior in Sport</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>10:20:00 - 12:00:00</t>
-  </si>
-  <si>
-    <t>Behavioral Methods</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Models of Change</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:55:00</t>
-  </si>
-  <si>
-    <t>Stochastic Behavior</t>
-  </si>
-  <si>
-    <t>Eli Specimen, Dee Placeholder</t>
-  </si>
-  <si>
-    <t>SectionId</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>AcademicYear</t>
-  </si>
-  <si>
-    <t>MinimumCredits</t>
-  </si>
-  <si>
-    <t>MaximumCredits</t>
-  </si>
-  <si>
-    <t>StartTime</t>
-  </si>
-  <si>
-    <t>MeetingDuration</t>
-  </si>
-  <si>
-    <t>Classroom</t>
-  </si>
-  <si>
-    <t>CourseLevel</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Enrollment</t>
-  </si>
-  <si>
-    <t>EnrollmentDay10</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV112-A</t>
-  </si>
-  <si>
-    <t>AY25</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV112-B</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV212-A</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV312-A</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>AY25-WI-BHAV121-A</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>AY25-SP-BHAV112-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-BHAV219-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-BHAV112-A</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>Load</t>
-  </si>
-  <si>
-    <t>AY</t>
-  </si>
-  <si>
-    <t>Constraint</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Course</t>
-  </si>
-  <si>
-    <t>Instructor</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Choose</t>
-  </si>
-  <si>
-    <t>Bound</t>
-  </si>
-  <si>
-    <t>Gap</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Starts</t>
-  </si>
-  <si>
-    <t>Days</t>
-  </si>
-  <si>
-    <t>DayRule</t>
-  </si>
-  <si>
-    <t>From</t>
-  </si>
-  <si>
-    <t>To</t>
-  </si>
-  <si>
-    <t>Should</t>
-  </si>
-  <si>
-    <t>Meets</t>
-  </si>
-  <si>
-    <t>Element</t>
-  </si>
-  <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Intensive terms meet daily</t>
-  </si>
-  <si>
-    <t>standard</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>WI, SU</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
-  </si>
-  <si>
-    <t>allow</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>StartWeek</t>
-  </si>
-  <si>
-    <t>EndWeek</t>
-  </si>
-  <si>
-    <t>SpreadTerm</t>
-  </si>
-  <si>
-    <t>NonRoom</t>
-  </si>
-  <si>
-    <t>Off Campus</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Fall</t>
-  </si>
-  <si>
     <t>Winter Intensive</t>
   </si>
   <si>
@@ -490,7 +490,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:51:36</t>
+    <t>12:17:43</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -1397,13 +1397,13 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
         <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
@@ -1418,22 +1418,22 @@
         <v>46</v>
       </c>
       <c r="H8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
         <v>38</v>
       </c>
       <c r="J8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L8">
         <v>150</v>
       </c>
       <c r="M8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N8" t="s">
         <v>28</v>
@@ -1471,7 +1471,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
         <v>34</v>
@@ -1483,10 +1483,10 @@
         <v>35</v>
       </c>
       <c r="G9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" t="s">
         <v>60</v>
-      </c>
-      <c r="H9" t="s">
-        <v>61</v>
       </c>
       <c r="I9" t="s">
         <v>38</v>
@@ -1501,7 +1501,7 @@
         <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N9" t="s">
         <v>28</v>
@@ -1539,7 +1539,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>
@@ -1551,10 +1551,10 @@
         <v>35</v>
       </c>
       <c r="G10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" t="s">
         <v>60</v>
-      </c>
-      <c r="H10" t="s">
-        <v>61</v>
       </c>
       <c r="I10" t="s">
         <v>38</v>
@@ -1569,7 +1569,7 @@
         <v>100</v>
       </c>
       <c r="M10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N10" t="s">
         <v>28</v>
@@ -1607,7 +1607,7 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
         <v>34</v>
@@ -1619,10 +1619,10 @@
         <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -1637,10 +1637,10 @@
         <v>100</v>
       </c>
       <c r="M11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" t="s">
         <v>67</v>
-      </c>
-      <c r="N11" t="s">
-        <v>68</v>
       </c>
       <c r="O11" t="s">
         <v>41</v>
@@ -1705,13 +1705,13 @@
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -1735,22 +1735,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -1759,10 +1759,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -1771,10 +1771,10 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>18</v>
@@ -1785,13 +1785,13 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>81</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>82</v>
       </c>
       <c r="D2" t="s">
         <v>22</v>
@@ -1824,7 +1824,7 @@
         <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O2">
         <v>65</v>
@@ -1865,13 +1865,13 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -1904,7 +1904,7 @@
         <v>36</v>
       </c>
       <c r="N3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O3">
         <v>65</v>
@@ -1945,13 +1945,13 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -1963,7 +1963,7 @@
         <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H4" t="s">
         <v>34</v>
@@ -1981,10 +1981,10 @@
         <v>23</v>
       </c>
       <c r="M4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -1993,7 +1993,7 @@
         <v>38</v>
       </c>
       <c r="Q4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R4" t="s">
         <v>41</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -2043,13 +2043,13 @@
         <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H5" t="s">
         <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -2061,10 +2061,10 @@
         <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -2073,7 +2073,7 @@
         <v>38</v>
       </c>
       <c r="Q5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R5" t="s">
         <v>41</v>
@@ -2105,25 +2105,25 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
         <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H6" t="s">
         <v>34</v>
@@ -2144,7 +2144,7 @@
         <v>46</v>
       </c>
       <c r="N6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O6">
         <v>150</v>
@@ -2153,7 +2153,7 @@
         <v>38</v>
       </c>
       <c r="Q6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R6" t="s">
         <v>41</v>
@@ -2185,13 +2185,13 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
         <v>30</v>
@@ -2224,7 +2224,7 @@
         <v>36</v>
       </c>
       <c r="N7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O7">
         <v>65</v>
@@ -2265,13 +2265,13 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
@@ -2283,7 +2283,7 @@
         <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H8" t="s">
         <v>34</v>
@@ -2301,10 +2301,10 @@
         <v>23</v>
       </c>
       <c r="M8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -2313,7 +2313,7 @@
         <v>38</v>
       </c>
       <c r="Q8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R8" t="s">
         <v>41</v>
@@ -2345,13 +2345,13 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>44</v>
@@ -2384,7 +2384,7 @@
         <v>46</v>
       </c>
       <c r="N9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O9">
         <v>150</v>
@@ -2441,7 +2441,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2468,19 +2468,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -2497,7 +2497,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2540,70 +2540,70 @@
   <sheetData>
     <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>16</v>
@@ -2611,82 +2611,82 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" t="s">
         <v>118</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>119</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
         <v>120</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" t="s">
         <v>121</v>
       </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>122</v>
-      </c>
-      <c r="W2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" t="s">
         <v>118</v>
       </c>
-      <c r="B3" t="s">
-        <v>119</v>
-      </c>
       <c r="C3" t="s">
         <v>23</v>
       </c>
@@ -2709,16 +2709,16 @@
         <v>23</v>
       </c>
       <c r="J3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K3" t="s">
         <v>124</v>
       </c>
-      <c r="K3" t="s">
-        <v>125</v>
-      </c>
       <c r="L3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N3" t="s">
         <v>46</v>
@@ -2745,7 +2745,7 @@
         <v>23</v>
       </c>
       <c r="V3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W3" t="s">
         <v>23</v>
@@ -2753,11 +2753,11 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" t="s">
         <v>118</v>
       </c>
-      <c r="B4" t="s">
-        <v>119</v>
-      </c>
       <c r="C4" t="s">
         <v>23</v>
       </c>
@@ -2780,16 +2780,16 @@
         <v>23</v>
       </c>
       <c r="J4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K4" t="s">
         <v>124</v>
       </c>
-      <c r="K4" t="s">
-        <v>125</v>
-      </c>
       <c r="L4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N4" t="s">
         <v>46</v>
@@ -2816,7 +2816,7 @@
         <v>23</v>
       </c>
       <c r="V4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W4" t="s">
         <v>23</v>
@@ -2841,27 +2841,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -2881,7 +2881,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
         <v>30</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" t="s">
         <v>132</v>
-      </c>
-      <c r="B4" t="s">
-        <v>133</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
@@ -2967,7 +2967,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -2984,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
         <v>136</v>
@@ -3190,7 +3190,7 @@
         <v>151</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -3243,12 +3243,12 @@
         <v>158</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -3275,7 +3275,7 @@
         <v>162</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">

--- a/apps/web/public/examples/example-merging-bhav.xlsx
+++ b/apps/web/public/examples/example-merging-bhav.xlsx
@@ -490,7 +490,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>12:17:43</t>
+    <t>14:23:18</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-merging-bhav.xlsx
+++ b/apps/web/public/examples/example-merging-bhav.xlsx
@@ -490,7 +490,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>14:23:18</t>
+    <t>15:09:00</t>
   </si>
   <si>
     <t>Academic Year</t>
